--- a/data_objects.xlsx
+++ b/data_objects.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ЭтаКнига" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hitot\Documents\pto-bot-v2-\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hitot\YandexDisk\Мои Документы\Прочее\Work\AutoDoc\Бот_ПТО\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F523C27-B4CA-4DF7-BC25-2D5CE9625714}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3123013-E974-4237-8E5E-3B03F1F2E57E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="690" xr2:uid="{F67A7888-32F2-483B-9005-9CE18BCF7DEE}"/>
   </bookViews>
@@ -177,9 +177,6 @@
     <t>Дата окончания работ по Заявке</t>
   </si>
   <si>
-    <t>Дата начала раболт по Заявке</t>
-  </si>
-  <si>
     <t>24-42580</t>
   </si>
   <si>
@@ -436,6 +433,9 @@
   </si>
   <si>
     <t>-1003826927197</t>
+  </si>
+  <si>
+    <t>Дата начала работ по Заявке</t>
   </si>
 </sst>
 </file>
@@ -915,7 +915,7 @@
     </row>
     <row r="2" spans="1:24" ht="40.799999999999997" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>34</v>
@@ -924,10 +924,10 @@
         <v>14</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>17</v>
@@ -945,7 +945,7 @@
         <v>44</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>46</v>
+        <v>132</v>
       </c>
       <c r="L2" s="5" t="s">
         <v>45</v>
@@ -954,37 +954,37 @@
         <v>15</v>
       </c>
       <c r="N2" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="O2" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="O2" s="11" t="s">
+      <c r="P2" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="P2" s="11" t="s">
+      <c r="Q2" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="Q2" s="5" t="s">
+      <c r="R2" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="R2" s="11" t="s">
+      <c r="S2" s="11" t="s">
         <v>121</v>
-      </c>
-      <c r="S2" s="11" t="s">
-        <v>122</v>
       </c>
       <c r="T2" s="5" t="s">
         <v>16</v>
       </c>
       <c r="U2" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="V2" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="V2" s="11" t="s">
+      <c r="W2" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="W2" s="11" t="s">
+      <c r="X2" s="11" t="s">
         <v>125</v>
-      </c>
-      <c r="X2" s="11" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="3" spans="1:24" ht="30.6" x14ac:dyDescent="0.3">
@@ -996,7 +996,7 @@
         <v>20</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>10</v>
@@ -1020,32 +1020,32 @@
         <v>37</v>
       </c>
       <c r="N3" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="O3" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="O3" s="13" t="s">
+      <c r="P3" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="P3" s="3" t="s">
+      <c r="Q3" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="Q3" s="12" t="s">
+      <c r="R3" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="R3" s="13" t="s">
-        <v>80</v>
-      </c>
       <c r="S3" s="13" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="T3" s="1" t="s">
         <v>8</v>
       </c>
       <c r="V3" s="16"/>
       <c r="W3" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="X3" s="17" t="s">
         <v>100</v>
-      </c>
-      <c r="X3" s="17" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="4" spans="1:24" ht="30.6" x14ac:dyDescent="0.3">
@@ -1057,7 +1057,7 @@
         <v>20</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>12</v>
@@ -1081,37 +1081,37 @@
         <v>39</v>
       </c>
       <c r="N4" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="O4" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="O4" s="13" t="s">
+      <c r="P4" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="P4" s="3" t="s">
+      <c r="Q4" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="Q4" s="12" t="s">
+      <c r="R4" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="R4" s="13" t="s">
-        <v>80</v>
-      </c>
       <c r="S4" s="13" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="T4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="V4" s="16"/>
       <c r="W4" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="X4" s="17" t="s">
         <v>100</v>
-      </c>
-      <c r="X4" s="17" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="5" spans="1:24" ht="40.799999999999997" x14ac:dyDescent="0.3">
       <c r="A5" s="19" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B5" s="3">
         <v>55</v>
@@ -1120,7 +1120,7 @@
         <v>21</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>32</v>
@@ -1144,37 +1144,37 @@
         <v>37</v>
       </c>
       <c r="N5" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="O5" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="O5" s="13" t="s">
+      <c r="P5" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="P5" s="3" t="s">
+      <c r="Q5" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="Q5" s="12" t="s">
+      <c r="R5" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="R5" s="13" t="s">
-        <v>80</v>
-      </c>
       <c r="S5" s="13" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="T5" s="1" t="s">
         <v>3</v>
       </c>
       <c r="U5" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="V5" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="V5" s="17" t="s">
+      <c r="W5" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="W5" s="18" t="s">
+      <c r="X5" s="17" t="s">
         <v>104</v>
-      </c>
-      <c r="X5" s="17" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="6" spans="1:24" ht="30.6" x14ac:dyDescent="0.3">
@@ -1186,7 +1186,7 @@
         <v>21</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>41</v>
@@ -1210,42 +1210,42 @@
         <v>38</v>
       </c>
       <c r="N6" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="O6" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="O6" s="13" t="s">
+      <c r="P6" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="P6" s="3" t="s">
-        <v>78</v>
-      </c>
       <c r="Q6" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="R6" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="R6" s="13" t="s">
-        <v>82</v>
-      </c>
       <c r="S6" s="13" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="T6" s="1" t="s">
         <v>3</v>
       </c>
       <c r="U6" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="V6" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="V6" s="17" t="s">
+      <c r="W6" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="W6" s="18" t="s">
+      <c r="X6" s="17" t="s">
         <v>104</v>
-      </c>
-      <c r="X6" s="17" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="7" spans="1:24" ht="30.6" x14ac:dyDescent="0.3">
       <c r="A7" s="19" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B7" s="3">
         <v>55</v>
@@ -1254,7 +1254,7 @@
         <v>21</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>0</v>
@@ -1278,37 +1278,37 @@
         <v>38</v>
       </c>
       <c r="N7" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="O7" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="O7" s="13" t="s">
+      <c r="P7" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="P7" s="3" t="s">
-        <v>78</v>
-      </c>
       <c r="Q7" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="R7" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="R7" s="13" t="s">
-        <v>82</v>
-      </c>
       <c r="S7" s="13" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="T7" s="1" t="s">
         <v>8</v>
       </c>
       <c r="U7" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="V7" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="V7" s="17" t="s">
+      <c r="W7" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="W7" s="18" t="s">
+      <c r="X7" s="17" t="s">
         <v>104</v>
-      </c>
-      <c r="X7" s="17" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="8" spans="1:24" ht="30.6" x14ac:dyDescent="0.3">
@@ -1320,13 +1320,13 @@
         <v>22</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E8" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F8" s="4" t="s">
         <v>48</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>49</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>43</v>
@@ -1338,7 +1338,7 @@
         <v>46386</v>
       </c>
       <c r="J8" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K8" s="10">
         <v>45649</v>
@@ -1360,15 +1360,15 @@
       </c>
       <c r="V8" s="16"/>
       <c r="W8" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="X8" s="17" t="s">
         <v>104</v>
-      </c>
-      <c r="X8" s="17" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="9" spans="1:24" ht="30.6" x14ac:dyDescent="0.3">
       <c r="A9" s="19" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B9" s="3">
         <v>95</v>
@@ -1377,13 +1377,13 @@
         <v>23</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E9" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="F9" s="4" t="s">
         <v>50</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>51</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>6</v>
@@ -1398,42 +1398,42 @@
         <v>38</v>
       </c>
       <c r="N9" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="O9" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="O9" s="13" t="s">
+      <c r="P9" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>78</v>
-      </c>
       <c r="Q9" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="R9" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="R9" s="13" t="s">
-        <v>82</v>
-      </c>
       <c r="S9" s="13" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="T9" s="1" t="s">
         <v>8</v>
       </c>
       <c r="U9" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="V9" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="V9" s="16" t="s">
-        <v>107</v>
-      </c>
       <c r="W9" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="X9" s="17" t="s">
         <v>104</v>
-      </c>
-      <c r="X9" s="17" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="10" spans="1:24" ht="30.6" x14ac:dyDescent="0.3">
       <c r="A10" s="19" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B10" s="3">
         <v>189</v>
@@ -1442,13 +1442,13 @@
         <v>24</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E10" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="F10" s="4" t="s">
         <v>52</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>53</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>5</v>
@@ -1463,37 +1463,37 @@
         <v>37</v>
       </c>
       <c r="N10" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="O10" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="O10" s="13" t="s">
+      <c r="P10" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="P10" s="3" t="s">
+      <c r="Q10" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="Q10" s="12" t="s">
+      <c r="R10" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="R10" s="13" t="s">
-        <v>87</v>
-      </c>
       <c r="S10" s="13" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="T10" s="1" t="s">
         <v>3</v>
       </c>
       <c r="U10" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="V10" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="V10" s="16" t="s">
-        <v>109</v>
-      </c>
       <c r="W10" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="X10" s="17" t="s">
         <v>100</v>
-      </c>
-      <c r="X10" s="17" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="11" spans="1:24" ht="40.799999999999997" x14ac:dyDescent="0.3">
@@ -1505,16 +1505,16 @@
         <v>25</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E11" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="F11" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="F11" s="4" t="s">
-        <v>57</v>
-      </c>
       <c r="G11" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H11" s="10">
         <v>45322</v>
@@ -1523,7 +1523,7 @@
         <v>46021</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K11" s="10">
         <v>45716</v>
@@ -1532,16 +1532,16 @@
         <v>46008</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="N11" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="O11" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="O11" s="13" t="s">
+      <c r="P11" s="3" t="s">
         <v>89</v>
-      </c>
-      <c r="P11" s="3" t="s">
-        <v>90</v>
       </c>
       <c r="Q11" s="12"/>
       <c r="R11" s="13"/>
@@ -1550,16 +1550,16 @@
         <v>3</v>
       </c>
       <c r="U11" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="V11" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="V11" s="16" t="s">
-        <v>111</v>
-      </c>
       <c r="W11" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="X11" s="17" t="s">
         <v>100</v>
-      </c>
-      <c r="X11" s="17" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="12" spans="1:24" ht="30.6" x14ac:dyDescent="0.3">
@@ -1571,7 +1571,7 @@
         <v>27</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E12" s="4" t="s">
         <v>1</v>
@@ -1589,32 +1589,32 @@
         <v>46022</v>
       </c>
       <c r="N12" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="O12" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="O12" s="13" t="s">
+      <c r="P12" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="P12" s="3" t="s">
-        <v>78</v>
-      </c>
       <c r="Q12" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="R12" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="R12" s="13" t="s">
-        <v>82</v>
-      </c>
       <c r="S12" s="13" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="T12" s="1" t="s">
         <v>3</v>
       </c>
       <c r="V12" s="16"/>
       <c r="W12" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="X12" s="17" t="s">
         <v>104</v>
-      </c>
-      <c r="X12" s="17" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="13" spans="1:24" ht="30.6" x14ac:dyDescent="0.3">
@@ -1626,16 +1626,16 @@
         <v>30</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H13" s="10">
         <v>45449</v>
@@ -1644,7 +1644,7 @@
         <v>46386</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K13" s="10">
         <v>45701</v>
@@ -1653,16 +1653,16 @@
         <v>46326</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="N13" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="O13" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="O13" s="13" t="s">
+      <c r="P13" s="3" t="s">
         <v>84</v>
-      </c>
-      <c r="P13" s="3" t="s">
-        <v>85</v>
       </c>
       <c r="Q13" s="14"/>
       <c r="R13" s="15"/>
@@ -1671,21 +1671,21 @@
         <v>3</v>
       </c>
       <c r="U13" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="V13" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="V13" s="16" t="s">
-        <v>111</v>
-      </c>
       <c r="W13" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="X13" s="17" t="s">
         <v>104</v>
-      </c>
-      <c r="X13" s="17" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="14" spans="1:24" ht="61.2" x14ac:dyDescent="0.3">
       <c r="A14" s="19" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B14" s="3">
         <v>850</v>
@@ -1694,16 +1694,16 @@
         <v>29</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E14" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="F14" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="G14" s="2" t="s">
         <v>71</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>72</v>
       </c>
       <c r="H14" s="10">
         <v>45791</v>
@@ -1724,16 +1724,16 @@
         <v>3</v>
       </c>
       <c r="U14" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="V14" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="V14" s="16" t="s">
-        <v>113</v>
-      </c>
       <c r="W14" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="X14" s="17" t="s">
         <v>104</v>
-      </c>
-      <c r="X14" s="17" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="15" spans="1:24" ht="40.799999999999997" x14ac:dyDescent="0.3">
@@ -1745,16 +1745,16 @@
         <v>28</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H15" s="10">
         <v>45791</v>
@@ -1775,16 +1775,16 @@
         <v>3</v>
       </c>
       <c r="U15" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="V15" s="16" t="s">
         <v>114</v>
       </c>
-      <c r="V15" s="16" t="s">
-        <v>115</v>
-      </c>
       <c r="W15" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="X15" s="17" t="s">
         <v>104</v>
-      </c>
-      <c r="X15" s="17" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="16" spans="1:24" ht="30.6" x14ac:dyDescent="0.3">
@@ -1796,16 +1796,16 @@
         <v>26</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E16" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="G16" s="2" t="s">
         <v>58</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>59</v>
       </c>
       <c r="H16" s="10">
         <v>46041</v>
@@ -1814,7 +1814,7 @@
         <v>46752</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="N16" s="12"/>
       <c r="O16" s="13"/>
@@ -1834,16 +1834,16 @@
         <v>207</v>
       </c>
       <c r="C17" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F17" s="4" t="s">
         <v>63</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>64</v>
       </c>
       <c r="H17" s="10"/>
       <c r="I17" s="10"/>
